--- a/data/20260915/Target Per Hari GLD5_2026-09-15_GLD5_TargetPerHari_20260914.xlsx
+++ b/data/20260915/Target Per Hari GLD5_2026-09-15_GLD5_TargetPerHari_20260914.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
   <si>
     <t>Date :</t>
   </si>
@@ -193,15 +193,6 @@
   </si>
   <si>
     <t>LINE 16-20</t>
-  </si>
-  <si>
-    <t>EQC</t>
-  </si>
-  <si>
-    <t>SELISIH</t>
-  </si>
-  <si>
-    <t>PERMINTAAN SCHEDULE</t>
   </si>
 </sst>
 </file>
@@ -252,7 +243,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -395,61 +386,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -483,6 +424,38 @@
     <xf numFmtId="166" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -499,53 +472,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -842,21 +768,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
-    <col min="5" max="6" width="8.7109375" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="9" width="8.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="8.7109375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -864,73 +786,61 @@
         <v>46279</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="13.5" thickBot="1"/>
-    <row r="3" spans="1:15" ht="13.5" thickTop="1">
-      <c r="A3" s="39" t="s">
+    <row r="2" spans="1:12" ht="13.5" thickBot="1"/>
+    <row r="3" spans="1:12" ht="13.5" customHeight="1" thickTop="1">
+      <c r="A3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="35" t="s">
+      <c r="E3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="F3" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="G3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="K3" s="35" t="s">
+      <c r="H3" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="35" t="s">
+      <c r="I3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="35" t="s">
+      <c r="J3" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="35" t="s">
+      <c r="K3" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="37" t="s">
+      <c r="L3" s="27" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="40"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="38"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="31" t="s">
+    <row r="4" spans="1:12">
+      <c r="A4" s="30"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="28"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="33" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -942,48 +852,38 @@
       <c r="D5" s="5">
         <v>14</v>
       </c>
-      <c r="E5" s="5">
-        <v>11</v>
-      </c>
-      <c r="F5" s="5">
-        <f>D5-E5</f>
-        <v>3</v>
-      </c>
-      <c r="G5" s="32">
+      <c r="E5" s="34">
         <v>9</v>
       </c>
-      <c r="H5" s="6">
-        <f>IF(G5=0,0,D5/G5)</f>
+      <c r="F5" s="6">
+        <f>IF(E5=0,0,D5/E5)</f>
         <v>1.5555555555555556</v>
       </c>
-      <c r="I5" s="33">
-        <f>IF(G5=0,0,SUMPRODUCT(H5:H7,M5:M7)/(L5*2.52))</f>
+      <c r="G5" s="35">
+        <f>IF(E5=0,0,SUMPRODUCT(F5:F7,J5:J7)/(I5*2.52))</f>
         <v>1.2157157157157159</v>
       </c>
-      <c r="J5" s="45">
-        <v>1.4</v>
-      </c>
-      <c r="K5" s="34">
-        <f>I5*L5*G5</f>
+      <c r="H5" s="36">
+        <f>G5*I5*E5</f>
         <v>404.83333333333337</v>
       </c>
-      <c r="L5" s="34">
+      <c r="I5" s="36">
         <v>37</v>
       </c>
-      <c r="M5" s="5">
+      <c r="J5" s="5">
         <v>0.8</v>
       </c>
-      <c r="N5" s="6">
-        <f>2.52/M5*L5</f>
+      <c r="K5" s="6">
+        <f>2.52/J5*I5</f>
         <v>116.55</v>
       </c>
-      <c r="O5" s="7">
-        <f>G5*L5</f>
+      <c r="L5" s="7">
+        <f>E5*I5</f>
         <v>333</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="31"/>
+    <row r="6" spans="1:12">
+      <c r="A6" s="33"/>
       <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
@@ -993,33 +893,25 @@
       <c r="D6" s="5">
         <v>1253</v>
       </c>
-      <c r="E6" s="5">
-        <v>1237</v>
-      </c>
-      <c r="F6" s="5">
-        <f t="shared" ref="F6:F31" si="0">D6-E6</f>
-        <v>16</v>
-      </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="6">
-        <f>IF(G5=0,0,D6/G5)</f>
+      <c r="E6" s="34"/>
+      <c r="F6" s="6">
+        <f>IF(E5=0,0,D6/E5)</f>
         <v>139.22222222222223</v>
       </c>
-      <c r="I6" s="33"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="5">
+      <c r="G6" s="35"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="5">
         <v>0.8</v>
       </c>
-      <c r="N6" s="6">
-        <f>2.52/M6*L5</f>
+      <c r="K6" s="6">
+        <f>2.52/J6*I5</f>
         <v>116.55</v>
       </c>
-      <c r="O6" s="7"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="31"/>
+      <c r="L6" s="7"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="33"/>
       <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
@@ -1029,32 +921,24 @@
       <c r="D7" s="5">
         <v>7</v>
       </c>
-      <c r="E7" s="5">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="6">
-        <f>IF(G5=0,0,D7/G5)</f>
+      <c r="E7" s="34"/>
+      <c r="F7" s="6">
+        <f>IF(E5=0,0,D7/E5)</f>
         <v>0.77777777777777779</v>
       </c>
-      <c r="I7" s="33"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="5">
+      <c r="G7" s="35"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="5">
         <v>0.94</v>
       </c>
-      <c r="N7" s="6">
-        <f>2.52/M7*L5</f>
+      <c r="K7" s="6">
+        <f>2.52/J7*I5</f>
         <v>99.191489361702125</v>
       </c>
-      <c r="O7" s="7"/>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="L7" s="7"/>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="8" t="s">
         <v>17</v>
       </c>
@@ -1067,47 +951,37 @@
       <c r="D8" s="5">
         <v>640</v>
       </c>
-      <c r="E8" s="5">
-        <v>633</v>
-      </c>
-      <c r="F8" s="5">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="G8" s="9">
+      <c r="E8" s="9">
         <v>8</v>
       </c>
-      <c r="H8" s="6">
-        <f>IF(G8=0,0,D8/G8)</f>
+      <c r="F8" s="6">
+        <f>IF(E8=0,0,D8/E8)</f>
         <v>80</v>
       </c>
-      <c r="I8" s="10">
-        <f>IF(G8=0,0,SUMPRODUCT(H8:H8,M8:M8)/(L8*2.52))</f>
+      <c r="G8" s="10">
+        <f>IF(E8=0,0,SUMPRODUCT(F8:F8,J8:J8)/(I8*2.52))</f>
         <v>1.3179413179413182</v>
       </c>
-      <c r="J8" s="10">
-        <v>1.2</v>
-      </c>
-      <c r="K8" s="11">
-        <f>I8*L8*G8</f>
+      <c r="H8" s="11">
+        <f>G8*I8*E8</f>
         <v>347.93650793650801</v>
       </c>
-      <c r="L8" s="11">
+      <c r="I8" s="11">
         <v>33</v>
       </c>
-      <c r="M8" s="5">
+      <c r="J8" s="5">
         <v>1.37</v>
       </c>
-      <c r="N8" s="6">
-        <f>2.52/M8*L8</f>
+      <c r="K8" s="6">
+        <f>2.52/J8*I8</f>
         <v>60.700729927007302</v>
       </c>
-      <c r="O8" s="7">
-        <f>G8*L8</f>
+      <c r="L8" s="7">
+        <f>E8*I8</f>
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:12">
       <c r="A9" s="8" t="s">
         <v>19</v>
       </c>
@@ -1120,47 +994,37 @@
       <c r="D9" s="5">
         <v>642</v>
       </c>
-      <c r="E9" s="5">
-        <v>632</v>
-      </c>
-      <c r="F9" s="5">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="G9" s="9">
+      <c r="E9" s="9">
         <v>9</v>
       </c>
-      <c r="H9" s="6">
-        <f>IF(G9=0,0,D9/G9)</f>
+      <c r="F9" s="6">
+        <f>IF(E9=0,0,D9/E9)</f>
         <v>71.333333333333329</v>
       </c>
-      <c r="I9" s="10">
-        <f>IF(G9=0,0,SUMPRODUCT(H9:H9,M9:M9)/(L9*2.52))</f>
+      <c r="G9" s="10">
+        <f>IF(E9=0,0,SUMPRODUCT(F9:F9,J9:J9)/(I9*2.52))</f>
         <v>1.3653906006847181</v>
       </c>
-      <c r="J9" s="10">
+      <c r="H9" s="11">
+        <f>G9*I9*E9</f>
+        <v>417.80952380952374</v>
+      </c>
+      <c r="I9" s="11">
+        <v>34</v>
+      </c>
+      <c r="J9" s="5">
         <v>1.64</v>
       </c>
-      <c r="K9" s="11">
-        <f>I9*L9*G9</f>
-        <v>417.80952380952374</v>
-      </c>
-      <c r="L9" s="11">
-        <v>34</v>
-      </c>
-      <c r="M9" s="5">
-        <v>1.64</v>
-      </c>
-      <c r="N9" s="6">
-        <f>2.52/M9*L9</f>
+      <c r="K9" s="6">
+        <f>2.52/J9*I9</f>
         <v>52.243902439024389</v>
       </c>
-      <c r="O9" s="7">
-        <f>G9*L9</f>
+      <c r="L9" s="7">
+        <f>E9*I9</f>
         <v>306</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:12">
       <c r="A10" s="8" t="s">
         <v>21</v>
       </c>
@@ -1173,48 +1037,38 @@
       <c r="D10" s="5">
         <v>1382</v>
       </c>
-      <c r="E10" s="5">
-        <v>1373</v>
-      </c>
-      <c r="F10" s="5">
-        <f t="shared" si="0"/>
+      <c r="E10" s="9">
         <v>9</v>
       </c>
-      <c r="G10" s="9">
-        <v>9</v>
-      </c>
-      <c r="H10" s="6">
-        <f>IF(G10=0,0,D10/G10)</f>
+      <c r="F10" s="6">
+        <f>IF(E10=0,0,D10/E10)</f>
         <v>153.55555555555554</v>
       </c>
-      <c r="I10" s="10">
-        <f>IF(G10=0,0,SUMPRODUCT(H10:H10,M10:M10)/(L10*2.52))</f>
+      <c r="G10" s="10">
+        <f>IF(E10=0,0,SUMPRODUCT(F10:F10,J10:J10)/(I10*2.52))</f>
         <v>1.5592125739184561</v>
       </c>
-      <c r="J10" s="10">
-        <v>1.4</v>
-      </c>
-      <c r="K10" s="11">
-        <f>I10*L10*G10</f>
+      <c r="H10" s="11">
+        <f>G10*I10*E10</f>
         <v>477.11904761904754</v>
       </c>
-      <c r="L10" s="11">
+      <c r="I10" s="11">
         <v>34</v>
       </c>
-      <c r="M10" s="5">
+      <c r="J10" s="5">
         <v>0.87</v>
       </c>
-      <c r="N10" s="6">
-        <f>2.52/M10*L10</f>
+      <c r="K10" s="6">
+        <f>2.52/J10*I10</f>
         <v>98.482758620689651</v>
       </c>
-      <c r="O10" s="7">
-        <f>G10*L10</f>
+      <c r="L10" s="7">
+        <f>E10*I10</f>
         <v>306</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="31" t="s">
+    <row r="11" spans="1:12">
+      <c r="A11" s="33" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -1226,48 +1080,38 @@
       <c r="D11" s="5">
         <v>636</v>
       </c>
-      <c r="E11" s="5">
-        <v>636</v>
-      </c>
-      <c r="F11" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" s="32">
+      <c r="E11" s="34">
         <v>8</v>
       </c>
-      <c r="H11" s="6">
-        <f>IF(G11=0,0,D11/G11)</f>
+      <c r="F11" s="6">
+        <f>IF(E11=0,0,D11/E11)</f>
         <v>79.5</v>
       </c>
-      <c r="I11" s="33">
-        <f>IF(G11=0,0,SUMPRODUCT(H11:H12,M11:M12)/(L11*2.52))</f>
+      <c r="G11" s="35">
+        <f>IF(E11=0,0,SUMPRODUCT(F11:F12,J11:J12)/(I11*2.52))</f>
         <v>1.9454365079365081</v>
       </c>
-      <c r="J11" s="45">
-        <v>2.1</v>
-      </c>
-      <c r="K11" s="34">
-        <f>I11*L11*G11</f>
+      <c r="H11" s="36">
+        <f>G11*I11*E11</f>
         <v>560.28571428571433</v>
       </c>
-      <c r="L11" s="34">
+      <c r="I11" s="36">
         <v>36</v>
       </c>
-      <c r="M11" s="5">
+      <c r="J11" s="5">
         <v>2.2200000000000002</v>
       </c>
-      <c r="N11" s="6">
-        <f>2.52/M11*L11</f>
+      <c r="K11" s="6">
+        <f>2.52/J11*I11</f>
         <v>40.864864864864863</v>
       </c>
-      <c r="O11" s="7">
-        <f>G11*L11</f>
+      <c r="L11" s="7">
+        <f>E11*I11</f>
         <v>288</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="31"/>
+    <row r="12" spans="1:12">
+      <c r="A12" s="33"/>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
@@ -1277,32 +1121,24 @@
       <c r="D12" s="5">
         <v>0</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="34"/>
+      <c r="F12" s="6">
+        <f>IF(E11=0,0,D12/E11)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="6">
-        <f>IF(G11=0,0,D12/G11)</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="33"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="5">
+      <c r="G12" s="35"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="N12" s="6">
-        <f>2.52/M12*L11</f>
+      <c r="K12" s="6">
+        <f>2.52/J12*I11</f>
         <v>39.443478260869568</v>
       </c>
-      <c r="O12" s="7"/>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="L12" s="7"/>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="8" t="s">
         <v>25</v>
       </c>
@@ -1315,47 +1151,37 @@
       <c r="D13" s="5">
         <v>28</v>
       </c>
-      <c r="E13" s="5">
-        <v>28</v>
-      </c>
-      <c r="F13" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="9">
+      <c r="E13" s="9">
         <v>8</v>
       </c>
-      <c r="H13" s="6">
-        <f>IF(G13=0,0,D13/G13)</f>
+      <c r="F13" s="6">
+        <f>IF(E13=0,0,D13/E13)</f>
         <v>3.5</v>
       </c>
-      <c r="I13" s="10">
-        <f>IF(G13=0,0,SUMPRODUCT(H13:H13,M13:M13)/(L13*2.52))</f>
+      <c r="G13" s="10">
+        <f>IF(E13=0,0,SUMPRODUCT(F13:F13,J13:J13)/(I13*2.52))</f>
         <v>4.1666666666666671E-2</v>
       </c>
-      <c r="J13" s="10">
-        <v>1</v>
-      </c>
-      <c r="K13" s="11">
-        <f>I13*L13*G13</f>
+      <c r="H13" s="11">
+        <f>G13*I13*E13</f>
         <v>11.666666666666668</v>
       </c>
-      <c r="L13" s="11">
+      <c r="I13" s="11">
         <v>35</v>
       </c>
-      <c r="M13" s="5">
+      <c r="J13" s="5">
         <v>1.05</v>
       </c>
-      <c r="N13" s="6">
-        <f>2.52/M13*L13</f>
+      <c r="K13" s="6">
+        <f>2.52/J13*I13</f>
         <v>84</v>
       </c>
-      <c r="O13" s="7">
-        <f>G13*L13</f>
+      <c r="L13" s="7">
+        <f>E13*I13</f>
         <v>280</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:12">
       <c r="A14" s="8" t="s">
         <v>27</v>
       </c>
@@ -1368,48 +1194,38 @@
       <c r="D14" s="5">
         <v>1318</v>
       </c>
-      <c r="E14" s="5">
-        <v>1321</v>
-      </c>
-      <c r="F14" s="5">
-        <f t="shared" si="0"/>
-        <v>-3</v>
-      </c>
-      <c r="G14" s="9">
+      <c r="E14" s="9">
         <v>9</v>
       </c>
-      <c r="H14" s="6">
-        <f>IF(G14=0,0,D14/G14)</f>
+      <c r="F14" s="6">
+        <f>IF(E14=0,0,D14/E14)</f>
         <v>146.44444444444446</v>
       </c>
-      <c r="I14" s="10">
-        <f>IF(G14=0,0,SUMPRODUCT(H14:H14,M14:M14)/(L14*2.52))</f>
+      <c r="G14" s="10">
+        <f>IF(E14=0,0,SUMPRODUCT(F14:F14,J14:J14)/(I14*2.52))</f>
         <v>1.2387218045112782</v>
       </c>
-      <c r="J14" s="10">
-        <v>1.3</v>
-      </c>
-      <c r="K14" s="11">
-        <f>I14*L14*G14</f>
+      <c r="H14" s="11">
+        <f>G14*I14*E14</f>
         <v>423.64285714285711</v>
       </c>
-      <c r="L14" s="11">
+      <c r="I14" s="11">
         <v>38</v>
       </c>
-      <c r="M14" s="5">
+      <c r="J14" s="5">
         <v>0.81</v>
       </c>
-      <c r="N14" s="6">
-        <f>2.52/M14*L14</f>
+      <c r="K14" s="6">
+        <f>2.52/J14*I14</f>
         <v>118.2222222222222</v>
       </c>
-      <c r="O14" s="7">
-        <f>G14*L14</f>
+      <c r="L14" s="7">
+        <f>E14*I14</f>
         <v>342</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="31" t="s">
+    <row r="15" spans="1:12">
+      <c r="A15" s="33" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1419,48 +1235,38 @@
       <c r="D15" s="5">
         <v>0</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="34">
+        <v>9</v>
+      </c>
+      <c r="F15" s="6">
+        <f>IF(E15=0,0,D15/E15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="32">
-        <v>9</v>
-      </c>
-      <c r="H15" s="6">
-        <f>IF(G15=0,0,D15/G15)</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="33">
-        <f>IF(G15=0,0,SUMPRODUCT(H15:H16,M15:M16)/(L15*2.52))</f>
+      <c r="G15" s="35">
+        <f>IF(E15=0,0,SUMPRODUCT(F15:F16,J15:J16)/(I15*2.52))</f>
         <v>0.59756515775034291</v>
       </c>
-      <c r="J15" s="45">
-        <v>1</v>
-      </c>
-      <c r="K15" s="34">
-        <f>I15*L15*G15</f>
+      <c r="H15" s="36">
+        <f>G15*I15*E15</f>
         <v>193.61111111111111</v>
       </c>
-      <c r="L15" s="34">
+      <c r="I15" s="36">
         <v>36</v>
       </c>
-      <c r="M15" s="5">
+      <c r="J15" s="5">
         <v>1.61</v>
       </c>
-      <c r="N15" s="6">
-        <f>2.52/M15*L15</f>
+      <c r="K15" s="6">
+        <f>2.52/J15*I15</f>
         <v>56.347826086956516</v>
       </c>
-      <c r="O15" s="7">
-        <f>G15*L15</f>
+      <c r="L15" s="7">
+        <f>E15*I15</f>
         <v>324</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="31"/>
+    <row r="16" spans="1:12">
+      <c r="A16" s="33"/>
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
@@ -1470,32 +1276,24 @@
       <c r="D16" s="5">
         <v>574</v>
       </c>
-      <c r="E16" s="5">
-        <v>567</v>
-      </c>
-      <c r="F16" s="5">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="6">
-        <f>IF(G15=0,0,D16/G15)</f>
+      <c r="E16" s="34"/>
+      <c r="F16" s="6">
+        <f>IF(E15=0,0,D16/E15)</f>
         <v>63.777777777777779</v>
       </c>
-      <c r="I16" s="33"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="5">
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="5">
         <v>0.85</v>
       </c>
-      <c r="N16" s="6">
-        <f>2.52/M16*L15</f>
+      <c r="K16" s="6">
+        <f>2.52/J16*I15</f>
         <v>106.72941176470589</v>
       </c>
-      <c r="O16" s="7"/>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="L16" s="7"/>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="8" t="s">
         <v>32</v>
       </c>
@@ -1508,47 +1306,37 @@
       <c r="D17" s="5">
         <v>650</v>
       </c>
-      <c r="E17" s="5">
-        <v>650</v>
-      </c>
-      <c r="F17" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="9">
+      <c r="E17" s="9">
         <v>9</v>
       </c>
-      <c r="H17" s="6">
-        <f>IF(G17=0,0,D17/G17)</f>
+      <c r="F17" s="6">
+        <f>IF(E17=0,0,D17/E17)</f>
         <v>72.222222222222229</v>
       </c>
-      <c r="I17" s="10">
-        <f>IF(G17=0,0,SUMPRODUCT(H17:H17,M17:M17)/(L17*2.52))</f>
+      <c r="G17" s="10">
+        <f>IF(E17=0,0,SUMPRODUCT(F17:F17,J17:J17)/(I17*2.52))</f>
         <v>1.466697790227202</v>
       </c>
-      <c r="J17" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="K17" s="11">
-        <f>I17*L17*G17</f>
+      <c r="H17" s="11">
+        <f>G17*I17*E17</f>
         <v>448.8095238095238</v>
       </c>
-      <c r="L17" s="11">
+      <c r="I17" s="11">
         <v>34</v>
       </c>
-      <c r="M17" s="5">
+      <c r="J17" s="5">
         <v>1.74</v>
       </c>
-      <c r="N17" s="6">
-        <f>2.52/M17*L17</f>
+      <c r="K17" s="6">
+        <f>2.52/J17*I17</f>
         <v>49.241379310344826</v>
       </c>
-      <c r="O17" s="7">
-        <f>G17*L17</f>
+      <c r="L17" s="7">
+        <f>E17*I17</f>
         <v>306</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:12">
       <c r="A18" s="8" t="s">
         <v>34</v>
       </c>
@@ -1561,48 +1349,38 @@
       <c r="D18" s="5">
         <v>1249</v>
       </c>
-      <c r="E18" s="5">
-        <v>1256</v>
-      </c>
-      <c r="F18" s="5">
-        <f t="shared" si="0"/>
-        <v>-7</v>
-      </c>
-      <c r="G18" s="9">
+      <c r="E18" s="9">
         <v>9</v>
       </c>
-      <c r="H18" s="6">
-        <f>IF(G18=0,0,D18/G18)</f>
+      <c r="F18" s="6">
+        <f>IF(E18=0,0,D18/E18)</f>
         <v>138.77777777777777</v>
       </c>
-      <c r="I18" s="10">
-        <f>IF(G18=0,0,SUMPRODUCT(H18:H18,M18:M18)/(L18*2.52))</f>
+      <c r="G18" s="10">
+        <f>IF(E18=0,0,SUMPRODUCT(F18:F18,J18:J18)/(I18*2.52))</f>
         <v>1.2115520282186949</v>
       </c>
-      <c r="J18" s="10">
-        <v>1.3</v>
-      </c>
-      <c r="K18" s="11">
-        <f>I18*L18*G18</f>
+      <c r="H18" s="11">
+        <f>G18*I18*E18</f>
         <v>381.63888888888891</v>
       </c>
-      <c r="L18" s="11">
+      <c r="I18" s="11">
         <v>35</v>
       </c>
-      <c r="M18" s="5">
+      <c r="J18" s="5">
         <v>0.77</v>
       </c>
-      <c r="N18" s="6">
-        <f>2.52/M18*L18</f>
+      <c r="K18" s="6">
+        <f>2.52/J18*I18</f>
         <v>114.54545454545453</v>
       </c>
-      <c r="O18" s="7">
-        <f>G18*L18</f>
+      <c r="L18" s="7">
+        <f>E18*I18</f>
         <v>315</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
-      <c r="A19" s="31" t="s">
+    <row r="19" spans="1:12">
+      <c r="A19" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1614,48 +1392,38 @@
       <c r="D19" s="5">
         <v>16</v>
       </c>
-      <c r="E19" s="5">
-        <v>11</v>
-      </c>
-      <c r="F19" s="5">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G19" s="32">
+      <c r="E19" s="34">
         <v>8</v>
       </c>
-      <c r="H19" s="6">
-        <f>IF(G19=0,0,D19/G19)</f>
+      <c r="F19" s="6">
+        <f>IF(E19=0,0,D19/E19)</f>
         <v>2</v>
       </c>
-      <c r="I19" s="33">
-        <f>IF(G19=0,0,SUMPRODUCT(H19:H20,M19:M20)/(L19*2.52))</f>
+      <c r="G19" s="35">
+        <f>IF(E19=0,0,SUMPRODUCT(F19:F20,J19:J20)/(I19*2.52))</f>
         <v>1.0966055341055343</v>
       </c>
-      <c r="J19" s="45">
-        <v>1</v>
-      </c>
-      <c r="K19" s="34">
-        <f>I19*L19*G19</f>
+      <c r="H19" s="36">
+        <f>G19*I19*E19</f>
         <v>324.59523809523813</v>
       </c>
-      <c r="L19" s="34">
+      <c r="I19" s="36">
         <v>37</v>
       </c>
-      <c r="M19" s="5">
+      <c r="J19" s="5">
         <v>2.2200000000000002</v>
       </c>
-      <c r="N19" s="6">
-        <f>2.52/M19*L19</f>
+      <c r="K19" s="6">
+        <f>2.52/J19*I19</f>
         <v>42</v>
       </c>
-      <c r="O19" s="7">
-        <f>G19*L19</f>
+      <c r="L19" s="7">
+        <f>E19*I19</f>
         <v>296</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="31"/>
+    <row r="20" spans="1:12">
+      <c r="A20" s="33"/>
       <c r="B20" s="3" t="s">
         <v>30</v>
       </c>
@@ -1665,32 +1433,24 @@
       <c r="D20" s="5">
         <v>486</v>
       </c>
-      <c r="E20" s="5">
-        <v>465</v>
-      </c>
-      <c r="F20" s="5">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="G20" s="32"/>
-      <c r="H20" s="6">
-        <f>IF(G19=0,0,D20/G19)</f>
+      <c r="E20" s="34"/>
+      <c r="F20" s="6">
+        <f>IF(E19=0,0,D20/E19)</f>
         <v>60.75</v>
       </c>
-      <c r="I20" s="33"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="5">
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="5">
         <v>1.61</v>
       </c>
-      <c r="N20" s="6">
-        <f>2.52/M20*L19</f>
+      <c r="K20" s="6">
+        <f>2.52/J20*I19</f>
         <v>57.91304347826086</v>
       </c>
-      <c r="O20" s="7"/>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="L20" s="7"/>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="8" t="s">
         <v>37</v>
       </c>
@@ -1703,47 +1463,37 @@
       <c r="D21" s="5">
         <v>665</v>
       </c>
-      <c r="E21" s="5">
-        <v>660</v>
-      </c>
-      <c r="F21" s="5">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G21" s="9">
+      <c r="E21" s="9">
         <v>9</v>
       </c>
-      <c r="H21" s="6">
-        <f>IF(G21=0,0,D21/G21)</f>
+      <c r="F21" s="6">
+        <f>IF(E21=0,0,D21/E21)</f>
         <v>73.888888888888886</v>
       </c>
-      <c r="I21" s="10">
-        <f>IF(G21=0,0,SUMPRODUCT(H21:H21,M21:M21)/(L21*2.52))</f>
+      <c r="G21" s="10">
+        <f>IF(E21=0,0,SUMPRODUCT(F21:F21,J21:J21)/(I21*2.52))</f>
         <v>0.9172206394428617</v>
       </c>
-      <c r="J21" s="10">
-        <v>1.39</v>
-      </c>
-      <c r="K21" s="11">
-        <f>I21*L21*G21</f>
+      <c r="H21" s="11">
+        <f>G21*I21*E21</f>
         <v>321.94444444444446</v>
       </c>
-      <c r="L21" s="11">
+      <c r="I21" s="11">
         <v>39</v>
       </c>
-      <c r="M21" s="5">
+      <c r="J21" s="5">
         <v>1.22</v>
       </c>
-      <c r="N21" s="6">
-        <f>2.52/M21*L21</f>
+      <c r="K21" s="6">
+        <f>2.52/J21*I21</f>
         <v>80.557377049180332</v>
       </c>
-      <c r="O21" s="7">
-        <f>G21*L21</f>
+      <c r="L21" s="7">
+        <f>E21*I21</f>
         <v>351</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:12">
       <c r="A22" s="8" t="s">
         <v>39</v>
       </c>
@@ -1756,48 +1506,38 @@
       <c r="D22" s="5">
         <v>1595</v>
       </c>
-      <c r="E22" s="5">
-        <v>1592</v>
-      </c>
-      <c r="F22" s="5">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G22" s="9">
+      <c r="E22" s="9">
         <v>9</v>
       </c>
-      <c r="H22" s="6">
-        <f>IF(G22=0,0,D22/G22)</f>
+      <c r="F22" s="6">
+        <f>IF(E22=0,0,D22/E22)</f>
         <v>177.22222222222223</v>
       </c>
-      <c r="I22" s="10">
-        <f>IF(G22=0,0,SUMPRODUCT(H22:H22,M22:M22)/(L22*2.52))</f>
+      <c r="G22" s="10">
+        <f>IF(E22=0,0,SUMPRODUCT(F22:F22,J22:J22)/(I22*2.52))</f>
         <v>1.5688169854836522</v>
       </c>
-      <c r="J22" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="K22" s="11">
-        <f>I22*L22*G22</f>
+      <c r="H22" s="11">
+        <f>G22*I22*E22</f>
         <v>550.65476190476193</v>
       </c>
-      <c r="L22" s="11">
+      <c r="I22" s="11">
         <v>39</v>
       </c>
-      <c r="M22" s="5">
+      <c r="J22" s="5">
         <v>0.87</v>
       </c>
-      <c r="N22" s="6">
-        <f>2.52/M22*L22</f>
+      <c r="K22" s="6">
+        <f>2.52/J22*I22</f>
         <v>112.96551724137932</v>
       </c>
-      <c r="O22" s="7">
-        <f>G22*L22</f>
+      <c r="L22" s="7">
+        <f>E22*I22</f>
         <v>351</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="31" t="s">
+    <row r="23" spans="1:12">
+      <c r="A23" s="33" t="s">
         <v>40</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -1809,48 +1549,38 @@
       <c r="D23" s="5">
         <v>37</v>
       </c>
-      <c r="E23" s="5">
-        <v>37</v>
-      </c>
-      <c r="F23" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="32">
+      <c r="E23" s="34">
         <v>9</v>
       </c>
-      <c r="H23" s="6">
-        <f>IF(G23=0,0,D23/G23)</f>
+      <c r="F23" s="6">
+        <f>IF(E23=0,0,D23/E23)</f>
         <v>4.1111111111111107</v>
       </c>
-      <c r="I23" s="33">
-        <f>IF(G23=0,0,SUMPRODUCT(H23:H24,M23:M24)/(L23*2.52))</f>
+      <c r="G23" s="35">
+        <f>IF(E23=0,0,SUMPRODUCT(F23:F24,J23:J24)/(I23*2.52))</f>
         <v>1.3386011324607818</v>
       </c>
-      <c r="J23" s="45">
-        <v>1.9</v>
-      </c>
-      <c r="K23" s="34">
-        <f>I23*L23*G23</f>
+      <c r="H23" s="36">
+        <f>G23*I23*E23</f>
         <v>457.8015873015874</v>
       </c>
-      <c r="L23" s="34">
+      <c r="I23" s="36">
         <v>38</v>
       </c>
-      <c r="M23" s="5">
+      <c r="J23" s="5">
         <v>1.28</v>
       </c>
-      <c r="N23" s="6">
-        <f>2.52/M23*L23</f>
+      <c r="K23" s="6">
+        <f>2.52/J23*I23</f>
         <v>74.8125</v>
       </c>
-      <c r="O23" s="7">
-        <f>G23*L23</f>
+      <c r="L23" s="7">
+        <f>E23*I23</f>
         <v>342</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="31"/>
+    <row r="24" spans="1:12">
+      <c r="A24" s="33"/>
       <c r="B24" s="3" t="s">
         <v>42</v>
       </c>
@@ -1860,33 +1590,25 @@
       <c r="D24" s="5">
         <v>851</v>
       </c>
-      <c r="E24" s="5">
-        <v>851</v>
-      </c>
-      <c r="F24" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="32"/>
-      <c r="H24" s="6">
-        <f>IF(G23=0,0,D24/G23)</f>
+      <c r="E24" s="34"/>
+      <c r="F24" s="6">
+        <f>IF(E23=0,0,D24/E23)</f>
         <v>94.555555555555557</v>
       </c>
-      <c r="I24" s="33"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="5">
+      <c r="G24" s="35"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="5">
         <v>1.3</v>
       </c>
-      <c r="N24" s="6">
-        <f>2.52/M24*L23</f>
+      <c r="K24" s="6">
+        <f>2.52/J24*I23</f>
         <v>73.661538461538456</v>
       </c>
-      <c r="O24" s="7"/>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="31" t="s">
+      <c r="L24" s="7"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="33" t="s">
         <v>43</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -1898,48 +1620,38 @@
       <c r="D25" s="5">
         <v>8</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="34">
         <v>8</v>
       </c>
-      <c r="F25" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="32">
-        <v>8</v>
-      </c>
-      <c r="H25" s="6">
-        <f>IF(G25=0,0,D25/G25)</f>
+      <c r="F25" s="6">
+        <f>IF(E25=0,0,D25/E25)</f>
         <v>1</v>
       </c>
-      <c r="I25" s="33">
-        <f>IF(G25=0,0,SUMPRODUCT(H25:H26,M25:M26)/(L25*2.52))</f>
+      <c r="G25" s="35">
+        <f>IF(E25=0,0,SUMPRODUCT(F25:F26,J25:J26)/(I25*2.52))</f>
         <v>1.2007722007722008</v>
       </c>
-      <c r="J25" s="45">
-        <v>1.5</v>
-      </c>
-      <c r="K25" s="34">
-        <f>I25*L25*G25</f>
+      <c r="H25" s="36">
+        <f>G25*I25*E25</f>
         <v>355.42857142857144</v>
       </c>
-      <c r="L25" s="34">
+      <c r="I25" s="36">
         <v>37</v>
       </c>
-      <c r="M25" s="5">
+      <c r="J25" s="5">
         <v>0.87</v>
       </c>
-      <c r="N25" s="6">
-        <f>2.52/M25*L25</f>
+      <c r="K25" s="6">
+        <f>2.52/J25*I25</f>
         <v>107.17241379310344</v>
       </c>
-      <c r="O25" s="7">
-        <f>G25*L25</f>
+      <c r="L25" s="7">
+        <f>E25*I25</f>
         <v>296</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="31"/>
+    <row r="26" spans="1:12">
+      <c r="A26" s="33"/>
       <c r="B26" s="3" t="s">
         <v>30</v>
       </c>
@@ -1949,32 +1661,24 @@
       <c r="D26" s="5">
         <v>552</v>
       </c>
-      <c r="E26" s="5">
-        <v>552</v>
-      </c>
-      <c r="F26" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="32"/>
-      <c r="H26" s="6">
-        <f>IF(G25=0,0,D26/G25)</f>
+      <c r="E26" s="34"/>
+      <c r="F26" s="6">
+        <f>IF(E25=0,0,D26/E25)</f>
         <v>69</v>
       </c>
-      <c r="I26" s="33"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="5">
+      <c r="G26" s="35"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="5">
         <v>1.61</v>
       </c>
-      <c r="N26" s="6">
-        <f>2.52/M26*L25</f>
+      <c r="K26" s="6">
+        <f>2.52/J26*I25</f>
         <v>57.91304347826086</v>
       </c>
-      <c r="O26" s="7"/>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="L26" s="7"/>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="8" t="s">
         <v>45</v>
       </c>
@@ -1987,47 +1691,37 @@
       <c r="D27" s="5">
         <v>1800</v>
       </c>
-      <c r="E27" s="5">
-        <v>1800</v>
-      </c>
-      <c r="F27" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="9">
+      <c r="E27" s="9">
         <v>9</v>
       </c>
-      <c r="H27" s="6">
-        <f>IF(G27=0,0,D27/G27)</f>
+      <c r="F27" s="6">
+        <f>IF(E27=0,0,D27/E27)</f>
         <v>200</v>
       </c>
-      <c r="I27" s="10">
-        <f>IF(G27=0,0,SUMPRODUCT(H27:H27,M27:M27)/(L27*2.52))</f>
+      <c r="G27" s="10">
+        <f>IF(E27=0,0,SUMPRODUCT(F27:F27,J27:J27)/(I27*2.52))</f>
         <v>1.6945516945516947</v>
       </c>
-      <c r="J27" s="10">
-        <v>1.7</v>
-      </c>
-      <c r="K27" s="11">
-        <f>I27*L27*G27</f>
+      <c r="H27" s="11">
+        <f>G27*I27*E27</f>
         <v>564.28571428571433</v>
       </c>
-      <c r="L27" s="11">
+      <c r="I27" s="11">
         <v>37</v>
       </c>
-      <c r="M27" s="5">
+      <c r="J27" s="5">
         <v>0.79</v>
       </c>
-      <c r="N27" s="6">
-        <f>2.52/M27*L27</f>
+      <c r="K27" s="6">
+        <f>2.52/J27*I27</f>
         <v>118.02531645569618</v>
       </c>
-      <c r="O27" s="7">
-        <f>G27*L27</f>
+      <c r="L27" s="7">
+        <f>E27*I27</f>
         <v>333</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:12">
       <c r="A28" s="8" t="s">
         <v>47</v>
       </c>
@@ -2040,47 +1734,37 @@
       <c r="D28" s="5">
         <v>59</v>
       </c>
-      <c r="E28" s="5">
-        <v>59</v>
-      </c>
-      <c r="F28" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="9">
+      <c r="E28" s="9">
         <v>8</v>
       </c>
-      <c r="H28" s="6">
-        <f>IF(G28=0,0,D28/G28)</f>
+      <c r="F28" s="6">
+        <f>IF(E28=0,0,D28/E28)</f>
         <v>7.375</v>
       </c>
-      <c r="I28" s="10">
-        <f>IF(G28=0,0,SUMPRODUCT(H28:H28,M28:M28)/(L28*2.52))</f>
+      <c r="G28" s="10">
+        <f>IF(E28=0,0,SUMPRODUCT(F28:F28,J28:J28)/(I28*2.52))</f>
         <v>0.16659035409035411</v>
       </c>
-      <c r="J28" s="10">
-        <v>1.68</v>
-      </c>
-      <c r="K28" s="11">
-        <f>I28*L28*G28</f>
+      <c r="H28" s="11">
+        <f>G28*I28*E28</f>
         <v>51.976190476190482</v>
       </c>
-      <c r="L28" s="11">
+      <c r="I28" s="11">
         <v>39</v>
       </c>
-      <c r="M28" s="5">
+      <c r="J28" s="5">
         <v>2.2200000000000002</v>
       </c>
-      <c r="N28" s="6">
-        <f>2.52/M28*L28</f>
+      <c r="K28" s="6">
+        <f>2.52/J28*I28</f>
         <v>44.270270270270267</v>
       </c>
-      <c r="O28" s="7">
-        <f>G28*L28</f>
+      <c r="L28" s="7">
+        <f>E28*I28</f>
         <v>312</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:12">
       <c r="A29" s="8" t="s">
         <v>48</v>
       </c>
@@ -2093,47 +1777,37 @@
       <c r="D29" s="5">
         <v>1148</v>
       </c>
-      <c r="E29" s="5">
-        <v>1143</v>
-      </c>
-      <c r="F29" s="5">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G29" s="9">
+      <c r="E29" s="9">
         <v>9</v>
       </c>
-      <c r="H29" s="6">
-        <f>IF(G29=0,0,D29/G29)</f>
+      <c r="F29" s="6">
+        <f>IF(E29=0,0,D29/E29)</f>
         <v>127.55555555555556</v>
       </c>
-      <c r="I29" s="10">
-        <f>IF(G29=0,0,SUMPRODUCT(H29:H29,M29:M29)/(L29*2.52))</f>
+      <c r="G29" s="10">
+        <f>IF(E29=0,0,SUMPRODUCT(F29:F29,J29:J29)/(I29*2.52))</f>
         <v>1.2424242424242427</v>
       </c>
-      <c r="J29" s="10">
-        <v>1.22</v>
-      </c>
-      <c r="K29" s="11">
-        <f>I29*L29*G29</f>
+      <c r="H29" s="11">
+        <f>G29*I29*E29</f>
         <v>369.00000000000006</v>
       </c>
-      <c r="L29" s="11">
+      <c r="I29" s="11">
         <v>33</v>
       </c>
-      <c r="M29" s="5">
+      <c r="J29" s="5">
         <v>0.81</v>
       </c>
-      <c r="N29" s="6">
-        <f>2.52/M29*L29</f>
+      <c r="K29" s="6">
+        <f>2.52/J29*I29</f>
         <v>102.66666666666666</v>
       </c>
-      <c r="O29" s="7">
-        <f>G29*L29</f>
+      <c r="L29" s="7">
+        <f>E29*I29</f>
         <v>297</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:12">
       <c r="A30" s="8" t="s">
         <v>49</v>
       </c>
@@ -2146,47 +1820,37 @@
       <c r="D30" s="5">
         <v>1485</v>
       </c>
-      <c r="E30" s="5">
-        <v>1485</v>
-      </c>
-      <c r="F30" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="9">
+      <c r="E30" s="9">
         <v>9</v>
       </c>
-      <c r="H30" s="6">
-        <f>IF(G30=0,0,D30/G30)</f>
+      <c r="F30" s="6">
+        <f>IF(E30=0,0,D30/E30)</f>
         <v>165</v>
       </c>
-      <c r="I30" s="10">
-        <f>IF(G30=0,0,SUMPRODUCT(H30:H30,M30:M30)/(L30*2.52))</f>
+      <c r="G30" s="10">
+        <f>IF(E30=0,0,SUMPRODUCT(F30:F30,J30:J30)/(I30*2.52))</f>
         <v>1.3784461152882206</v>
       </c>
-      <c r="J30" s="10">
-        <v>1.4</v>
-      </c>
-      <c r="K30" s="11">
-        <f>I30*L30*G30</f>
+      <c r="H30" s="11">
+        <f>G30*I30*E30</f>
         <v>471.42857142857144</v>
       </c>
-      <c r="L30" s="11">
+      <c r="I30" s="11">
         <v>38</v>
       </c>
-      <c r="M30" s="5">
+      <c r="J30" s="5">
         <v>0.8</v>
       </c>
-      <c r="N30" s="6">
-        <f>2.52/M30*L30</f>
+      <c r="K30" s="6">
+        <f>2.52/J30*I30</f>
         <v>119.7</v>
       </c>
-      <c r="O30" s="7">
-        <f>G30*L30</f>
+      <c r="L30" s="7">
+        <f>E30*I30</f>
         <v>342</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:12">
       <c r="A31" s="8" t="s">
         <v>50</v>
       </c>
@@ -2199,241 +1863,199 @@
       <c r="D31" s="5">
         <v>695</v>
       </c>
-      <c r="E31" s="5">
-        <v>704</v>
-      </c>
-      <c r="F31" s="5">
-        <f t="shared" si="0"/>
-        <v>-9</v>
-      </c>
-      <c r="G31" s="9">
+      <c r="E31" s="9">
         <v>9</v>
       </c>
-      <c r="H31" s="6">
-        <f>IF(G31=0,0,D31/G31)</f>
+      <c r="F31" s="6">
+        <f>IF(E31=0,0,D31/E31)</f>
         <v>77.222222222222229</v>
       </c>
-      <c r="I31" s="10">
-        <f>IF(G31=0,0,SUMPRODUCT(H31:H31,M31:M31)/(L31*2.52))</f>
+      <c r="G31" s="10">
+        <f>IF(E31=0,0,SUMPRODUCT(F31:F31,J31:J31)/(I31*2.52))</f>
         <v>1.0912160708908676</v>
       </c>
-      <c r="J31" s="10">
-        <v>1</v>
-      </c>
-      <c r="K31" s="11">
-        <f>I31*L31*G31</f>
+      <c r="H31" s="11">
+        <f>G31*I31*E31</f>
         <v>402.65873015873012</v>
       </c>
-      <c r="L31" s="11">
+      <c r="I31" s="11">
         <v>41</v>
       </c>
-      <c r="M31" s="5">
+      <c r="J31" s="5">
         <v>1.46</v>
       </c>
-      <c r="N31" s="6">
-        <f>2.52/M31*L31</f>
+      <c r="K31" s="6">
+        <f>2.52/J31*I31</f>
         <v>70.767123287671239</v>
       </c>
-      <c r="O31" s="7">
-        <f>G31*L31</f>
+      <c r="L31" s="7">
+        <f>E31*I31</f>
         <v>369</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="25" t="s">
+    <row r="32" spans="1:12">
+      <c r="A32" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="27"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
       <c r="D32" s="12">
         <f>SUM(D5:D31)</f>
         <v>17790</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="13">
         <f>SUM(E5:E31)</f>
-        <v>17718</v>
-      </c>
-      <c r="F32" s="12">
-        <f>F14+F18+F31</f>
-        <v>-19</v>
-      </c>
-      <c r="G32" s="13">
-        <f>SUM(G5:G31)</f>
         <v>174</v>
       </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15">
-        <f>SUM(K5:K31)/O32</f>
+      <c r="F32" s="14"/>
+      <c r="G32" s="15">
+        <f>SUM(H5:H31)/L32</f>
         <v>1.1863886327919071</v>
       </c>
-      <c r="J32" s="15"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12">
+      <c r="H32" s="12"/>
+      <c r="I32" s="12">
+        <f>SUM(I5:I31)</f>
+        <v>730</v>
+      </c>
+      <c r="J32" s="12"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="16">
         <f>SUM(L5:L31)</f>
-        <v>730</v>
-      </c>
-      <c r="M32" s="12"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="16">
-        <f>SUM(O5:O31)</f>
         <v>6353</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:12">
       <c r="A33" s="17"/>
       <c r="B33" s="5"/>
       <c r="C33" s="4"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="7"/>
-    </row>
-    <row r="34" spans="1:15" ht="13.5" thickBot="1">
-      <c r="A34" s="28" t="s">
+      <c r="E33" s="18"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="7"/>
+    </row>
+    <row r="34" spans="1:12" ht="13.5" thickBot="1">
+      <c r="A34" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="29"/>
-      <c r="C34" s="30"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="42"/>
       <c r="D34" s="20">
         <f>SUMIF(A5:A33, "&lt;&gt;Summary", D5:D33)</f>
         <v>17790</v>
       </c>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="21">
-        <f>SUMIF(A5:A33, "&lt;&gt;Summary", G5:G33)</f>
+      <c r="E34" s="21">
+        <f>SUMIF(A5:A33, "&lt;&gt;Summary", E5:E33)</f>
         <v>174</v>
       </c>
-      <c r="H34" s="22"/>
-      <c r="I34" s="23">
-        <f>SUMIF(A5:A33, "&lt;&gt;Summary", K5:K33)/O34</f>
+      <c r="F34" s="22"/>
+      <c r="G34" s="23">
+        <f>SUMIF(A5:A33, "&lt;&gt;Summary", H5:H33)/L34</f>
         <v>1.1863886327919071</v>
       </c>
-      <c r="J34" s="23"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20">
+      <c r="H34" s="20"/>
+      <c r="I34" s="20">
+        <f>SUMIF(A5:A33, "&lt;&gt;Summary", I5:I33)</f>
+        <v>730</v>
+      </c>
+      <c r="J34" s="20"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="24">
         <f>SUMIF(A5:A33, "&lt;&gt;Summary", L5:L33)</f>
-        <v>730</v>
-      </c>
-      <c r="M34" s="20"/>
-      <c r="N34" s="22"/>
-      <c r="O34" s="24">
-        <f>SUMIF(A5:A33, "&lt;&gt;Summary", O5:O33)</f>
         <v>6353</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="13.5" thickTop="1"/>
-    <row r="36" spans="1:15">
-      <c r="C36" s="41" t="s">
+    <row r="35" spans="1:12" ht="13.5" thickTop="1"/>
+    <row r="36" spans="1:12">
+      <c r="C36" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="42">
-        <f>SUM(K5:K12)/SUM(O5:O12)</f>
+      <c r="D36" s="26">
+        <f>SUM(H5:H12)/SUM(L5:L12)</f>
         <v>1.4749392965825834</v>
       </c>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-    </row>
-    <row r="37" spans="1:15">
-      <c r="C37" s="41" t="s">
+    </row>
+    <row r="37" spans="1:12">
+      <c r="C37" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="42">
-        <f>SUM(K13:K18)/SUM(O13:O18)</f>
+      <c r="D37" s="26">
+        <f>SUM(H13:H18)/SUM(L13:L18)</f>
         <v>0.93131400613851156</v>
       </c>
-      <c r="E37" s="42"/>
-      <c r="F37" s="42"/>
-    </row>
-    <row r="38" spans="1:15">
-      <c r="C38" s="41" t="s">
+    </row>
+    <row r="38" spans="1:12">
+      <c r="C38" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="42">
-        <f>SUM(K19:K26)/SUM(O19:O26)</f>
+      <c r="D38" s="26">
+        <f>SUM(H19:H26)/SUM(L19:L26)</f>
         <v>1.2288658943610045</v>
       </c>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-    </row>
-    <row r="39" spans="1:15">
-      <c r="C39" s="41" t="s">
+    </row>
+    <row r="39" spans="1:12">
+      <c r="C39" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="D39" s="42">
-        <f>SUM(K27:K31)/SUM(O27:O31)</f>
+      <c r="D39" s="26">
+        <f>SUM(H27:H31)/SUM(L27:L31)</f>
         <v>1.1248331556861502</v>
       </c>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="O3:O4"/>
+  <mergeCells count="44">
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="L3:L4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="I3:I4"/>
     <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="K5:K7"/>
-    <mergeCell ref="L5:L7"/>
-    <mergeCell ref="J5:J7"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="I23:I24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="1" bottom="0.2" header="0.2" footer="0.2"/>
-  <pageSetup paperSize="9" scale="70" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;16PT GLORY DEMAK INDONESIA&amp;20
 TARGET PER HARI</oddHeader>
